--- a/7500 lpse.xlsx
+++ b/7500 lpse.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kerja\2025\SF2026\Matching SF dengan LKPP dan SIJK\LKPP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\projek\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{359C0F4E-F744-4AAC-8CE7-236AEA86F5B8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A941613-4D5F-4CF6-8A06-978BA1C7AE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" xr2:uid="{6FFB287C-A8A0-461D-9098-809041BA5663}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6FFB287C-A8A0-461D-9098-809041BA5663}"/>
   </bookViews>
   <sheets>
     <sheet name="75" sheetId="1" r:id="rId1"/>
@@ -469,12 +469,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -504,11 +516,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -824,9 +838,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7104142C-58C5-48A9-84D7-8728954F080E}">
   <dimension ref="A1:T30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -888,7 +924,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -935,7 +971,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -976,45 +1012,45 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="F4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>52</v>
       </c>
@@ -1058,201 +1094,201 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="F6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="H6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="Q6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="R6" t="s">
+      <c r="R6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="S6" t="s">
+      <c r="S6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="T6" t="s">
+      <c r="T6" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="F7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="H7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="Q7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="R7" t="s">
+      <c r="R7" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="S7" t="s">
+      <c r="S7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="T7" t="s">
+      <c r="T7" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="F8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="H8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="Q8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="R8" t="s">
+      <c r="R8" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="S8" t="s">
+      <c r="S8" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="T8" t="s">
+      <c r="T8" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="F9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H9" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="H9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M9" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N9" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>74</v>
       </c>
@@ -1296,136 +1332,136 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="F11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H11" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="H11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="M11" t="s">
+      <c r="M11" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="N11" t="s">
+      <c r="N11" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="F12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I12" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="H12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="M12" t="s">
+      <c r="M12" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="N12" t="s">
+      <c r="N12" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="13" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="F13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="H13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="L13" t="s">
-        <v>28</v>
-      </c>
-      <c r="M13" t="s">
+      <c r="L13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M13" s="3" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>93</v>
       </c>
@@ -1475,7 +1511,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>93</v>
       </c>
@@ -1525,121 +1561,121 @@
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="16" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="F16" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="F16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H16" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="H16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="L16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="L16" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="F17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="F17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I17" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" t="s">
+      <c r="H17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="L17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="L17" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="F18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="F18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="H18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="L18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L18" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>103</v>
       </c>
@@ -1680,92 +1716,92 @@
         <v>107</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="20" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F20" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="F20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="H20" t="s">
-        <v>27</v>
-      </c>
-      <c r="I20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="H20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L20" t="s">
+      <c r="L20" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M20" t="s">
+      <c r="M20" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="21" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F21" t="s">
-        <v>25</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="F21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H21" t="s">
-        <v>27</v>
-      </c>
-      <c r="I21" t="s">
-        <v>28</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="H21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="L21" t="s">
-        <v>28</v>
-      </c>
-      <c r="M21" t="s">
+      <c r="L21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M21" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="N21" t="s">
+      <c r="N21" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>119</v>
       </c>
@@ -1806,57 +1842,57 @@
         <v>123</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="23" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F23" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="F23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H23" t="s">
-        <v>27</v>
-      </c>
-      <c r="I23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J23" t="s">
+      <c r="H23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K23" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="L23" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q23" t="s">
+      <c r="L23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q23" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="R23" t="s">
+      <c r="R23" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="S23" t="s">
+      <c r="S23" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="T23" t="s">
+      <c r="T23" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>130</v>
       </c>
@@ -1894,7 +1930,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>124</v>
       </c>
@@ -1944,7 +1980,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>124</v>
       </c>
@@ -1994,7 +2030,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>130</v>
       </c>
@@ -2032,7 +2068,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -2076,7 +2112,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>99</v>
       </c>
@@ -2114,7 +2150,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>134</v>
       </c>
